--- a/TimeSheet.xlsx
+++ b/TimeSheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ricar\Rico's Stuff\School\Courses\CEN3907C\GatorBall\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{44146933-195F-4D39-8B7E-DC9031FE5333}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF07B9E-4F2B-477A-BF78-06A463DDBB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-78" yWindow="0" windowWidth="11676" windowHeight="12318" xr2:uid="{77B2A7E5-546A-4757-B1AA-4CBC7061E180}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{77B2A7E5-546A-4757-B1AA-4CBC7061E180}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Time Tracker</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>Design Draft</t>
+  </si>
+  <si>
+    <t>Did research on the visual interface portion of our project; the esp32 UWB tag</t>
+  </si>
+  <si>
+    <t>Brain stormed ideas for the physical interface and did some research for the programming interface</t>
   </si>
 </sst>
 </file>
@@ -116,13 +122,15 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17E4DD38-271C-4458-A607-7129C925B94E}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.68359375" customWidth="1"/>
@@ -446,31 +454,31 @@
     <col min="3" max="3" width="12.9453125" customWidth="1"/>
     <col min="4" max="4" width="19.3125" customWidth="1"/>
     <col min="5" max="5" width="15.734375" customWidth="1"/>
-    <col min="6" max="6" width="23.734375" customWidth="1"/>
+    <col min="6" max="6" width="23.734375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="56.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>45566</v>
       </c>
       <c r="C2" t="s">
@@ -482,12 +490,12 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B3" s="4">
+    <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" s="3">
         <v>45569</v>
       </c>
       <c r="C3" t="s">
@@ -498,6 +506,26 @@
       </c>
       <c r="E3" t="s">
         <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" s="3">
+        <v>45570</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/TimeSheet.xlsx
+++ b/TimeSheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ricar\Rico's Stuff\School\Courses\CEN3907C\GatorBall\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF07B9E-4F2B-477A-BF78-06A463DDBB4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5FACA8-2FAD-4E30-AA17-8B93A9761810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{77B2A7E5-546A-4757-B1AA-4CBC7061E180}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
   <si>
     <t>Time Tracker</t>
   </si>
@@ -70,6 +70,18 @@
   </si>
   <si>
     <t>Brain stormed ideas for the physical interface and did some research for the programming interface</t>
+  </si>
+  <si>
+    <t>Added my current ideas to the current Design Draft</t>
+  </si>
+  <si>
+    <t>1.5 hours</t>
+  </si>
+  <si>
+    <t>Worked together on the Design Draft; specifically worked on the Interface and Storyboard sections</t>
+  </si>
+  <si>
+    <t>Everyone + Lucas</t>
   </si>
 </sst>
 </file>
@@ -120,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -131,6 +143,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -446,11 +464,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17E4DD38-271C-4458-A607-7129C925B94E}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="15.68359375" customWidth="1"/>
-    <col min="2" max="2" width="13.7890625" customWidth="1"/>
+    <col min="2" max="2" width="13.7890625" style="6" customWidth="1"/>
     <col min="3" max="3" width="12.9453125" customWidth="1"/>
     <col min="4" max="4" width="19.3125" customWidth="1"/>
     <col min="5" max="5" width="15.734375" customWidth="1"/>
@@ -461,7 +479,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -526,6 +544,51 @@
       </c>
       <c r="F4" s="2" t="s">
         <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" s="3">
+        <v>45571</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" s="3">
+        <v>45572</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="B7" s="3">
+        <v>45573</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
